--- a/Bai_tap_SUM_AVERAGE_ROUND_NguyenMinhTuan.xlsx
+++ b/Bai_tap_SUM_AVERAGE_ROUND_NguyenMinhTuan.xlsx
@@ -8,12 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PTIT.BT\Tin_hoc_co_so_1\Bai_tap_phan_Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C6BD4CE-CE23-4712-A553-3DF953A74FEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D525277-006E-40A3-BB31-AD45727DB6D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{763D51E0-E6D5-472B-9A93-993C6412A1EE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="3" xr2:uid="{763D51E0-E6D5-472B-9A93-993C6412A1EE}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Bai1_DiemTB" sheetId="2" r:id="rId1"/>
+    <sheet name="Bai2_DoanhThu" sheetId="3" r:id="rId2"/>
+    <sheet name="Bai3_Luong" sheetId="4" r:id="rId3"/>
+    <sheet name="Bai4_TrongSo" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -58,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="33">
   <si>
     <t>Họ tên</t>
   </si>
@@ -94,6 +97,69 @@
   </si>
   <si>
     <t>Chi</t>
+  </si>
+  <si>
+    <t>Tổng điểm</t>
+  </si>
+  <si>
+    <t>Trung bình</t>
+  </si>
+  <si>
+    <t>TB làm tròn</t>
+  </si>
+  <si>
+    <t>Dũng</t>
+  </si>
+  <si>
+    <t>Hoa</t>
+  </si>
+  <si>
+    <t>Nhân viên</t>
+  </si>
+  <si>
+    <t>Tháng 1</t>
+  </si>
+  <si>
+    <t>Tháng 2</t>
+  </si>
+  <si>
+    <t>Tháng 3</t>
+  </si>
+  <si>
+    <t>Doanh thu lớn nhất</t>
+  </si>
+  <si>
+    <t>Doanh thu nhỏ nhất</t>
+  </si>
+  <si>
+    <t>Số tháng có doanh thu lớn hơn 10,000,000</t>
+  </si>
+  <si>
+    <t>Hạnh</t>
+  </si>
+  <si>
+    <t>Linh</t>
+  </si>
+  <si>
+    <t>Nam</t>
+  </si>
+  <si>
+    <t>Quân</t>
+  </si>
+  <si>
+    <t>Lương cơ bản</t>
+  </si>
+  <si>
+    <t>Phụ cấp</t>
+  </si>
+  <si>
+    <t>Thưởng</t>
+  </si>
+  <si>
+    <t>Tổng thu nhập</t>
+  </si>
+  <si>
+    <t>Thu nhập TB</t>
   </si>
 </sst>
 </file>
@@ -157,7 +223,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -166,6 +232,23 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -499,6 +582,466 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{759ADCC0-034E-42DC-A8F3-82B08B776501}">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="8.77734375" customWidth="1"/>
+    <col min="5" max="5" width="12.21875" customWidth="1"/>
+    <col min="6" max="6" width="13.109375" customWidth="1"/>
+    <col min="7" max="7" width="14.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="5">
+        <v>8</v>
+      </c>
+      <c r="C2" s="5">
+        <v>7</v>
+      </c>
+      <c r="D2" s="5">
+        <v>9</v>
+      </c>
+      <c r="E2" s="5">
+        <f>SUM(B2:D2)</f>
+        <v>24</v>
+      </c>
+      <c r="F2" s="5">
+        <f>AVERAGE(B2:D2)</f>
+        <v>8</v>
+      </c>
+      <c r="G2" s="5">
+        <f>ROUND(F2,0)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="5">
+        <v>6</v>
+      </c>
+      <c r="C3" s="5">
+        <v>5</v>
+      </c>
+      <c r="D3" s="5">
+        <v>7</v>
+      </c>
+      <c r="E3" s="5">
+        <f t="shared" ref="E3:E6" si="0">SUM(B3:D3)</f>
+        <v>18</v>
+      </c>
+      <c r="F3" s="5">
+        <f t="shared" ref="F3:F6" si="1">AVERAGE(B3:D3)</f>
+        <v>6</v>
+      </c>
+      <c r="G3" s="5">
+        <f t="shared" ref="G3:G6" si="2">ROUND(F3,0)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="5">
+        <v>9</v>
+      </c>
+      <c r="C4" s="5">
+        <v>9</v>
+      </c>
+      <c r="D4" s="5">
+        <v>8</v>
+      </c>
+      <c r="E4" s="5">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="F4" s="5">
+        <f t="shared" si="1"/>
+        <v>8.6666666666666661</v>
+      </c>
+      <c r="G4" s="5">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="5">
+        <v>5</v>
+      </c>
+      <c r="C5" s="5">
+        <v>6</v>
+      </c>
+      <c r="D5" s="5">
+        <v>6</v>
+      </c>
+      <c r="E5" s="5">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="F5" s="5">
+        <f t="shared" si="1"/>
+        <v>5.666666666666667</v>
+      </c>
+      <c r="G5" s="5">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="5">
+        <v>10</v>
+      </c>
+      <c r="C6" s="5">
+        <v>9</v>
+      </c>
+      <c r="D6" s="5">
+        <v>10</v>
+      </c>
+      <c r="E6" s="5">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="F6" s="5">
+        <f t="shared" si="1"/>
+        <v>9.6666666666666661</v>
+      </c>
+      <c r="G6" s="5">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAD8F0FF-5AA5-47C4-AAB9-E14B55937724}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="15.21875" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="12.77734375" customWidth="1"/>
+    <col min="5" max="5" width="24.21875" customWidth="1"/>
+    <col min="6" max="6" width="25.5546875" customWidth="1"/>
+    <col min="7" max="7" width="44.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="8">
+        <v>12500000</v>
+      </c>
+      <c r="C2" s="8">
+        <v>14200000</v>
+      </c>
+      <c r="D2" s="8">
+        <v>13800000</v>
+      </c>
+      <c r="E2" s="8">
+        <f>MAX(B2:D2)</f>
+        <v>14200000</v>
+      </c>
+      <c r="F2" s="8">
+        <f>MIN(B2:D2)</f>
+        <v>12500000</v>
+      </c>
+      <c r="G2" s="7">
+        <f>COUNTIF(B2:D2,"&gt;10000000")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="8">
+        <v>10000000</v>
+      </c>
+      <c r="C3" s="8">
+        <v>11500000</v>
+      </c>
+      <c r="D3" s="8">
+        <v>9800000</v>
+      </c>
+      <c r="E3" s="8">
+        <f t="shared" ref="E3:E5" si="0">MAX(B3:D3)</f>
+        <v>11500000</v>
+      </c>
+      <c r="F3" s="8">
+        <f t="shared" ref="F3:F5" si="1">MIN(B3:D3)</f>
+        <v>9800000</v>
+      </c>
+      <c r="G3" s="7">
+        <f t="shared" ref="G3:G5" si="2">COUNTIF(B3:D3,"&gt;10000000")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="8">
+        <v>15600000</v>
+      </c>
+      <c r="C4" s="8">
+        <v>16200000</v>
+      </c>
+      <c r="D4" s="8">
+        <v>15800000</v>
+      </c>
+      <c r="E4" s="8">
+        <f t="shared" si="0"/>
+        <v>16200000</v>
+      </c>
+      <c r="F4" s="8">
+        <f t="shared" si="1"/>
+        <v>15600000</v>
+      </c>
+      <c r="G4" s="7">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="8">
+        <v>8500000</v>
+      </c>
+      <c r="C5" s="8">
+        <v>9200000</v>
+      </c>
+      <c r="D5" s="8">
+        <v>10000000</v>
+      </c>
+      <c r="E5" s="8">
+        <f t="shared" si="0"/>
+        <v>10000000</v>
+      </c>
+      <c r="F5" s="8">
+        <f t="shared" si="1"/>
+        <v>8500000</v>
+      </c>
+      <c r="G5" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F37E176-E2A2-49A3-8149-9524AFED5054}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.5546875" customWidth="1"/>
+    <col min="2" max="2" width="18.21875" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" customWidth="1"/>
+    <col min="4" max="4" width="14.33203125" customWidth="1"/>
+    <col min="5" max="5" width="17.5546875" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" customWidth="1"/>
+    <col min="7" max="7" width="16.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="12">
+        <v>6000000</v>
+      </c>
+      <c r="C2" s="12">
+        <v>500000</v>
+      </c>
+      <c r="D2" s="12">
+        <v>1000000</v>
+      </c>
+      <c r="E2" s="12">
+        <f>SUM(B2:D2)</f>
+        <v>7500000</v>
+      </c>
+      <c r="F2" s="12">
+        <f>AVERAGE(B2:D2)</f>
+        <v>2500000</v>
+      </c>
+      <c r="G2" s="12">
+        <f>ROUND(F2,-3)</f>
+        <v>2500000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="12">
+        <v>7000000</v>
+      </c>
+      <c r="C3" s="12">
+        <v>1000000</v>
+      </c>
+      <c r="D3" s="12">
+        <v>800000</v>
+      </c>
+      <c r="E3" s="12">
+        <f t="shared" ref="E3:E5" si="0">SUM(B3:D3)</f>
+        <v>8800000</v>
+      </c>
+      <c r="F3" s="12">
+        <f t="shared" ref="F3:F5" si="1">AVERAGE(B3:D3)</f>
+        <v>2933333.3333333335</v>
+      </c>
+      <c r="G3" s="12">
+        <f t="shared" ref="G3:G5" si="2">ROUND(F3,-3)</f>
+        <v>2933000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="12">
+        <v>5500000</v>
+      </c>
+      <c r="C4" s="12">
+        <v>700000</v>
+      </c>
+      <c r="D4" s="12">
+        <v>500000</v>
+      </c>
+      <c r="E4" s="12">
+        <f t="shared" si="0"/>
+        <v>6700000</v>
+      </c>
+      <c r="F4" s="12">
+        <f t="shared" si="1"/>
+        <v>2233333.3333333335</v>
+      </c>
+      <c r="G4" s="12">
+        <f t="shared" si="2"/>
+        <v>2233000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="12">
+        <v>8000000</v>
+      </c>
+      <c r="C5" s="12">
+        <v>500000</v>
+      </c>
+      <c r="D5" s="12">
+        <v>2000000</v>
+      </c>
+      <c r="E5" s="12">
+        <f t="shared" si="0"/>
+        <v>10500000</v>
+      </c>
+      <c r="F5" s="12">
+        <f t="shared" si="1"/>
+        <v>3500000</v>
+      </c>
+      <c r="G5" s="12">
+        <f t="shared" si="2"/>
+        <v>3500000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC32CF20-D727-4C80-8FCD-FE206CA47C3F}">
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/Bai_tap_SUM_AVERAGE_ROUND_NguyenMinhTuan.xlsx
+++ b/Bai_tap_SUM_AVERAGE_ROUND_NguyenMinhTuan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PTIT.BT\Tin_hoc_co_so_1\Bai_tap_phan_Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D525277-006E-40A3-BB31-AD45727DB6D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD2668CB-21B3-4EDA-BE50-6A7E97D2F897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="3" xr2:uid="{763D51E0-E6D5-472B-9A93-993C6412A1EE}"/>
+    <workbookView xWindow="2376" yWindow="1476" windowWidth="17280" windowHeight="9276" xr2:uid="{763D51E0-E6D5-472B-9A93-993C6412A1EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Bai1_DiemTB" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="34">
   <si>
     <t>Họ tên</t>
   </si>
@@ -160,6 +160,9 @@
   </si>
   <si>
     <t>Thu nhập TB</t>
+  </si>
+  <si>
+    <t>Kết quả</t>
   </si>
 </sst>
 </file>
@@ -223,7 +226,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -232,23 +235,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -583,166 +573,190 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{759ADCC0-034E-42DC-A8F3-82B08B776501}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="8.77734375" customWidth="1"/>
     <col min="5" max="5" width="12.21875" customWidth="1"/>
     <col min="6" max="6" width="13.109375" customWidth="1"/>
     <col min="7" max="7" width="14.88671875" customWidth="1"/>
+    <col min="8" max="8" width="12.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="H1" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="2">
         <v>8</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="2">
         <v>7</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="2">
         <v>9</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="2">
         <f>SUM(B2:D2)</f>
         <v>24</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="2">
         <f>AVERAGE(B2:D2)</f>
         <v>8</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="2">
         <f>ROUND(F2,0)</f>
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="H2" s="2" t="str">
+        <f>IF(G2&gt;=5,"Đạt","Không đạt")</f>
+        <v>Đạt</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="2">
         <v>6</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="2">
         <v>5</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="2">
         <v>7</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="2">
         <f t="shared" ref="E3:E6" si="0">SUM(B3:D3)</f>
         <v>18</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="2">
         <f t="shared" ref="F3:F6" si="1">AVERAGE(B3:D3)</f>
         <v>6</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="2">
         <f t="shared" ref="G3:G6" si="2">ROUND(F3,0)</f>
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="H3" s="2" t="str">
+        <f t="shared" ref="H3:H6" si="3">IF(G3&gt;=5,"Đạt","Không đạt")</f>
+        <v>Đạt</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="2">
         <v>9</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="2">
         <v>9</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="2">
         <v>8</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="2">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="2">
         <f t="shared" si="1"/>
         <v>8.6666666666666661</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="2">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="H4" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>Đạt</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="2">
         <v>5</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="2">
         <v>6</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="2">
         <v>6</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="2">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="2">
         <f t="shared" si="1"/>
         <v>5.666666666666667</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="2">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="H5" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>Đạt</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="2">
         <v>10</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="2">
         <v>9</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="2">
         <v>10</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="2">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="2">
         <f t="shared" si="1"/>
         <v>9.6666666666666661</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="2">
         <f t="shared" si="2"/>
         <v>10</v>
+      </c>
+      <c r="H6" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>Đạt</v>
       </c>
     </row>
   </sheetData>
@@ -764,128 +778,128 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="4">
         <v>12500000</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="4">
         <v>14200000</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="4">
         <v>13800000</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="4">
         <f>MAX(B2:D2)</f>
         <v>14200000</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="4">
         <f>MIN(B2:D2)</f>
         <v>12500000</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="2">
         <f>COUNTIF(B2:D2,"&gt;10000000")</f>
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="4">
         <v>10000000</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="4">
         <v>11500000</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="4">
         <v>9800000</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="4">
         <f t="shared" ref="E3:E5" si="0">MAX(B3:D3)</f>
         <v>11500000</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="4">
         <f t="shared" ref="F3:F5" si="1">MIN(B3:D3)</f>
         <v>9800000</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="2">
         <f t="shared" ref="G3:G5" si="2">COUNTIF(B3:D3,"&gt;10000000")</f>
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="4">
         <v>15600000</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="4">
         <v>16200000</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="4">
         <v>15800000</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="4">
         <f t="shared" si="0"/>
         <v>16200000</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="4">
         <f t="shared" si="1"/>
         <v>15600000</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="2">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="4">
         <v>8500000</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="4">
         <v>9200000</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="4">
         <v>10000000</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="4">
         <f t="shared" si="0"/>
         <v>10000000</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="4">
         <f t="shared" si="1"/>
         <v>8500000</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -910,128 +924,128 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="4">
         <v>6000000</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="4">
         <v>500000</v>
       </c>
-      <c r="D2" s="12">
+      <c r="D2" s="4">
         <v>1000000</v>
       </c>
-      <c r="E2" s="12">
+      <c r="E2" s="4">
         <f>SUM(B2:D2)</f>
         <v>7500000</v>
       </c>
-      <c r="F2" s="12">
+      <c r="F2" s="4">
         <f>AVERAGE(B2:D2)</f>
         <v>2500000</v>
       </c>
-      <c r="G2" s="12">
+      <c r="G2" s="4">
         <f>ROUND(F2,-3)</f>
         <v>2500000</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="4">
         <v>7000000</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="4">
         <v>1000000</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="4">
         <v>800000</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="4">
         <f t="shared" ref="E3:E5" si="0">SUM(B3:D3)</f>
         <v>8800000</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="4">
         <f t="shared" ref="F3:F5" si="1">AVERAGE(B3:D3)</f>
         <v>2933333.3333333335</v>
       </c>
-      <c r="G3" s="12">
+      <c r="G3" s="4">
         <f t="shared" ref="G3:G5" si="2">ROUND(F3,-3)</f>
         <v>2933000</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="4">
         <v>5500000</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="4">
         <v>700000</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="4">
         <v>500000</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="4">
         <f t="shared" si="0"/>
         <v>6700000</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="4">
         <f t="shared" si="1"/>
         <v>2233333.3333333335</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="4">
         <f t="shared" si="2"/>
         <v>2233000</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="4">
         <v>8000000</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="4">
         <v>500000</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="4">
         <v>2000000</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="4">
         <f t="shared" si="0"/>
         <v>10500000</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="4">
         <f t="shared" si="1"/>
         <v>3500000</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="4">
         <f t="shared" si="2"/>
         <v>3500000</v>
       </c>
